--- a/docs/Planning détaillé.xlsx
+++ b/docs/Planning détaillé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27d5916ca408fb47/Documents/Projets_Python/Application de voyage familiale/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{050C420C-0EA5-4C5A-8A69-1D324746EF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50B891D6-5A5E-45C2-9647-BF5B9CFE94A4}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{050C420C-0EA5-4C5A-8A69-1D324746EF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79B07E52-6AFC-4173-921D-3FD7BC2A026E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{005EF8E4-31B8-4E21-8F79-E333B526983E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="67">
   <si>
     <t>LUNDI 17</t>
   </si>
@@ -153,30 +153,6 @@
   </si>
   <si>
     <t>Hypothèse 3 (moins probable) : ordre des étapes mélangé</t>
-  </si>
-  <si>
-    <r>
-      <t>Départ de l'hôtel avec le groupe pour découvrir le Grand Bazar,  le plus grand marché couvert du monde avec ses 4000 boutiques et le « Bazar Egyptien », le marché aux épices d’Istanbul . Nous aurons également la possibilité d’effectuer une promenade en bateau privé sur le Bosphore (si pas encore faite), occasion unique de contempler les yalis, prestigieuses résidences en bois et d’admirer les splendides façades des palais de Dolmabahce et de Beylerbeyi avec leur architecture XIX</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>ème</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t> siècle. Ou sinon nous pourrons visiter un des lieux non encore vus parmi ceux emblématiques de la ville. Après le déjeuner, départ pour Ankara (450 km), la capitale et la deuxième plus grande ville de Turquie. Dîner à l'hôtel (à confirmer)</t>
-    </r>
   </si>
   <si>
     <t>Départ en famille pleine nuit pour un tour en montgolfière (ou sinon ça sera le jour 6, selon météo et programme sur place) pour admirer les cheminées de fées et les paysages irréels de cette région. Cette excursion inoubliable présente à elle seule l’intérêt de ce voyage exceptionnel. La journée se poursuivra avec le groupe et sera dédiée à la découverte de la Cappadoce, site naturel unique au monde et berceau de la chrétienté. Son paysage ensorcelant et insolite où se dressent de gigantesques cheminées de fées qui ont conservé leurs grands chapeaux de basalte, vous impressionnera. Puis visite du musée en plein air de Göreme, classé Patrimoine Mondial de l’UNESCO, il abrite plusieurs églises rupestres ornées de fresques de la période byzantine. Nous découvrirons les splendides vallées d’Avcilar et de Guvercinlik où se dressent d’innombrables cheminées de fées aux surprenants aspects humain et animal. Arrêt  dans une boutique locale de bijoux et un centre artisanal de tapis où vous serez conquis par la créativité et la patience des femmes anatoliennes. Pour le soir : Kaira rooftop &amp; restaurant =&gt; pas de résa possible : y aller vers 17h30/18h pour être sûr d’avoir une place pour 5 et profiter du coucher du soleil - Possible réservation au Happena restaurant (réserver à partir du 11 aout)</t>
@@ -261,13 +237,20 @@
   </si>
   <si>
     <t xml:space="preserve">Restaurant à réserver : vers Taksim ? ou vers l'hôtel en rooftop ?) - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Bazar,  le plus grand marché couvert du monde avec ses 4000 boutiques et le « Bazar Egyptien », le marché aux épices d’Istanbul . 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Après le déjeuner, départ pour Ankara (450 km), la capitale et la deuxième plus grande ville de Turquie. Dîner à l'hôtel (à confirmer)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,13 +259,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos"/>
@@ -393,6 +369,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -712,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116894D-0342-4378-9C31-9BA7185975AD}">
-  <dimension ref="A2:E31"/>
+  <dimension ref="A2:E32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.109375" customWidth="1"/>
@@ -743,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>30</v>
@@ -760,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -773,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -786,7 +766,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>2</v>
@@ -803,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -816,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -829,7 +809,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -842,7 +822,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -855,7 +835,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -868,7 +848,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -881,7 +861,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -894,7 +874,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -907,7 +887,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -920,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -933,7 +913,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>6</v>
@@ -950,7 +930,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -963,7 +943,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -976,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -989,7 +969,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -1002,12 +982,12 @@
         <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="1:5" ht="126.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>7</v>
       </c>
@@ -1015,7 +995,7 @@
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>9</v>
@@ -1024,114 +1004,127 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="234.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
+        <v>45717</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="234.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5">
-        <v>45717</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E31" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
+    <row r="32" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Planning détaillé.xlsx
+++ b/docs/Planning détaillé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27d5916ca408fb47/Documents/Projets_Python/Application de voyage familiale/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{050C420C-0EA5-4C5A-8A69-1D324746EF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79B07E52-6AFC-4173-921D-3FD7BC2A026E}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{050C420C-0EA5-4C5A-8A69-1D324746EF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6E007E2-2C02-4654-9CAC-AFD357FAB26C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{005EF8E4-31B8-4E21-8F79-E333B526983E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="89">
   <si>
     <t>LUNDI 17</t>
   </si>
@@ -155,24 +155,7 @@
     <t>Hypothèse 3 (moins probable) : ordre des étapes mélangé</t>
   </si>
   <si>
-    <t>Départ en famille pleine nuit pour un tour en montgolfière (ou sinon ça sera le jour 6, selon météo et programme sur place) pour admirer les cheminées de fées et les paysages irréels de cette région. Cette excursion inoubliable présente à elle seule l’intérêt de ce voyage exceptionnel. La journée se poursuivra avec le groupe et sera dédiée à la découverte de la Cappadoce, site naturel unique au monde et berceau de la chrétienté. Son paysage ensorcelant et insolite où se dressent de gigantesques cheminées de fées qui ont conservé leurs grands chapeaux de basalte, vous impressionnera. Puis visite du musée en plein air de Göreme, classé Patrimoine Mondial de l’UNESCO, il abrite plusieurs églises rupestres ornées de fresques de la période byzantine. Nous découvrirons les splendides vallées d’Avcilar et de Guvercinlik où se dressent d’innombrables cheminées de fées aux surprenants aspects humain et animal. Arrêt  dans une boutique locale de bijoux et un centre artisanal de tapis où vous serez conquis par la créativité et la patience des femmes anatoliennes. Pour le soir : Kaira rooftop &amp; restaurant =&gt; pas de résa possible : y aller vers 17h30/18h pour être sûr d’avoir une place pour 5 et profiter du coucher du soleil - Possible réservation au Happena restaurant (réserver à partir du 11 aout)</t>
-  </si>
-  <si>
-    <t>Possible tour en montgolfière (si pas fait la veille) en famille.
-Après le petit-déjeuner, départ pour Konya (240 km), vous voyagerez à la rencontre de la fameuse route de la soie, jalonnée de nombreux vestiges de caravansérails. Vous serez émerveillés par les paysages sublimes du haut plateau de l’Anatolie Centrale. Arrêt photo devant un caravansérail Seldjoukide.
- Continuation pour Pamukkale et déjeuner en cours de route (420 km). Visite du site naturel de Pamukkale inscrit sur la liste du patrimoine mondial de l’UNESCO. Vous visiterez les célèbres « Châteaux de Coton » d’une blancheur éclatante où le ruissellement des sources d’eau chaude, saturées en sels calcaires a tapissé la falaise. Dîner libre (restaurant à réserver)</t>
-  </si>
-  <si>
-    <t>Après le petit-déjeuner, départ avec le groupe pour Ephese (180 km). La cité d’Artémis, site antique le plus célèbre de toute la Turquie, la rue des Courètes, la fameuse bibliothèque de Celsius, le temple d’Hadrien, la fontaine de Trajan, le splendide théâtre de 24 000 spectateurs et les vestiges du temple d’Artémis qui fait partie des sept merveilles du monde. Par ailleurs, cette cité était chère à l’apôtre Paul, il y séjourna plusieurs années. Déjeuner à Selcuk. Dans la journée, nous assisterons à un défilé de mode de cuir. Dîner libre (restaurant à réserver)</t>
-  </si>
-  <si>
-    <t>Après le petit-déjeuner, départ avec le groupe pour Bursa (360 km), la première capitale de l’Empire  Ottoman située au pied de l’antique Mont Olympe (Uludag). Visite de la Mosquée Verte et du Mausolée Vert, des tombeaux des sultans de la dynastie ottomane. Déjeuner. Continuation pour Istanbul (150 km)  en traversant le célèbre pont d’Osmangazi. Dîner libre (restaurant à réserver, dans le coin de l'hôtel ?)</t>
-  </si>
-  <si>
     <t>Cappadoce (montgolfière possible)</t>
-  </si>
-  <si>
-    <t>Après le petit déjeuner, départ de l'hôtel avec le groupe et visite du mausolée d'Atatürk, père de la Turquie moderne. Déjeuner et continuation pour la Cappadoce (320 km) à travers une plaine où miroite le lac salé. Nous explorerons également  une des nombreuses villes souterraines byzantines, refuge des autochtones entre le VIIème et le Xème siècle. Dîner à l'hôtel (à confirmer) ? ou sinon, réservation faite au Haruna restaurant à 19:15 - à libérer pour 21h15) RESA a priori annulée par le restau (à confirmer). Nouvelle résa faite au NANA RESTAURANT à 21h15</t>
   </si>
   <si>
     <t>Jour 10</t>
@@ -244,6 +227,88 @@
   </si>
   <si>
     <t xml:space="preserve"> Après le déjeuner, départ pour Ankara (450 km), la capitale et la deuxième plus grande ville de Turquie. Dîner à l'hôtel (à confirmer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déjeuner et continuation pour la Cappadoce (320 km) à travers une plaine où miroite le lac salé. Nous explorerons également  une des nombreuses villes souterraines byzantines, refuge des autochtones entre le VIIème et le Xème siècle. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mausolée d'Atatürk, père de la Turquie moderne. Dîner à l'hôtel (à confirmer) ? ou sinon, réservation faite au Haruna restaurant à 19:15 - à libérer pour 21h15) </t>
+  </si>
+  <si>
+    <t>RESA a priori annulée par le restau (à confirmer). Nouvelle résa faite au NANA RESTAURANT à 21h15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Départ en famille pleine nuit pour un tour en montgolfière (ou sinon ça sera le jour 6, selon météo et programme sur place) pour admirer les cheminées de fées et les paysages irréels de cette région. Cette excursion inoubliable présente à elle seule l’intérêt de ce voyage exceptionnel. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La journée se poursuivra avec le groupe et sera dédiée à la découverte de la Cappadoce, site naturel unique au monde et berceau de la chrétienté. Son paysage ensorcelant et insolite où se dressent de gigantesques cheminées de fées qui ont conservé leurs grands chapeaux de basalte, vous impressionnera. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puis visite du musée en plein air de Göreme, classé Patrimoine Mondial de l’UNESCO, il abrite plusieurs églises rupestres ornées de fresques de la période byzantine. </t>
+  </si>
+  <si>
+    <t>Nous découvrirons les splendides vallées d’Avcilar et de Guvercinlik où se dressent d’innombrables cheminées de fées aux surprenants aspects humain et animal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Arrêt  dans une boutique locale de bijoux et un centre artisanal de tapis où vous serez conquis par la créativité et la patience des femmes anatoliennes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pour le soir : Kaira rooftop &amp; restaurant =&gt; pas de résa possible : y aller vers 17h30/18h pour être sûr d’avoir une place pour 5 et profiter du coucher du soleil - Possible réservation au Happena restaurant (réserver à partir du 11 aout)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après le petit-déjeuner, départ pour Konya (240 km), vous voyagerez à la rencontre de la fameuse route de la soie, jalonnée de nombreux vestiges de caravansérails. Vous serez émerveillés par les paysages sublimes du haut plateau de l’Anatolie Centrale. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrêt photo devant un caravansérail Seldjoukide.
+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuation pour Pamukkale et déjeuner en cours de route (420 km). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visite du site naturel de Pamukkale inscrit sur la liste du patrimoine mondial de l’UNESCO. Vous visiterez les célèbres « Châteaux de Coton » d’une blancheur éclatante où le ruissellement des sources d’eau chaude, saturées en sels calcaires a tapissé la falaise. </t>
+  </si>
+  <si>
+    <t>Dîner libre (restaurant à réserver)</t>
+  </si>
+  <si>
+    <t>Après le petit-déjeuner, départ avec le groupe pour Ephese (180 km). La cité d’Artémis, site antique le plus célèbre de toute la Turquie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">, la rue des Courètes, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">la fameuse bibliothèque de Celsius, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">le temple d’Hadrien, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">la fontaine de Trajan, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">le splendide théâtre de 24 000 spectateurs et les vestiges du temple d’Artémis qui fait partie des sept merveilles du monde. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dîner libre (restaurant à réserver)</t>
+  </si>
+  <si>
+    <t>Déjeuner à Selcuk.</t>
+  </si>
+  <si>
+    <t>Après le petit-déjeuner, départ avec le groupe pour Bursa (360 km), la première capitale de l’Empire  Ottoman située au pied de l’antique Mont Olympe (Uludag).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Visite de la Mosquée Verte et du Mausolée Vert, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">des tombeaux des sultans de la dynastie ottomane. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuation pour Istanbul (150 km)  en traversant le célèbre pont d’Osmangazi. </t>
+  </si>
+  <si>
+    <t>Dîner libre (restaurant à réserver, dans le coin de l'hôtel ?)</t>
   </si>
 </sst>
 </file>
@@ -265,12 +330,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -337,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -352,6 +423,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -692,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116894D-0342-4378-9C31-9BA7185975AD}">
-  <dimension ref="A2:E32"/>
+  <dimension ref="A2:E54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.109375" customWidth="1"/>
@@ -716,14 +793,14 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>30</v>
@@ -733,40 +810,40 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>2</v>
@@ -776,144 +853,144 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>6</v>
@@ -923,79 +1000,79 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:5" ht="63" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>9</v>
@@ -1005,19 +1082,19 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="1:5" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>11</v>
       </c>
@@ -1025,7 +1102,7 @@
         <v>15</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>32</v>
@@ -1034,97 +1111,383 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="234.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="C29" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="63" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="5">
-        <v>45717</v>
+        <v>66</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+    </row>
+    <row r="50" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+    </row>
+    <row r="52" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="5">
+        <v>45717</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="3"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Planning détaillé.xlsx
+++ b/docs/Planning détaillé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27d5916ca408fb47/Documents/Projets_Python/Application de voyage familiale/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{050C420C-0EA5-4C5A-8A69-1D324746EF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6E007E2-2C02-4654-9CAC-AFD357FAB26C}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{050C420C-0EA5-4C5A-8A69-1D324746EF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2805053-88D2-441C-BBA6-084120670D78}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{005EF8E4-31B8-4E21-8F79-E333B526983E}"/>
   </bookViews>
@@ -330,7 +330,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,6 +340,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -422,13 +428,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -793,10 +802,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -810,10 +819,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -823,10 +832,10 @@
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -836,10 +845,10 @@
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -853,10 +862,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -866,10 +875,10 @@
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -879,10 +888,10 @@
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -892,10 +901,10 @@
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -905,10 +914,10 @@
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -918,10 +927,10 @@
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -931,10 +940,10 @@
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -944,10 +953,10 @@
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -957,10 +966,10 @@
       <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -970,10 +979,10 @@
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -983,10 +992,10 @@
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -1000,10 +1009,10 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -1013,10 +1022,10 @@
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -1026,10 +1035,10 @@
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -1039,10 +1048,10 @@
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:5" ht="63" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -1052,10 +1061,10 @@
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -1065,10 +1074,10 @@
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -1082,10 +1091,10 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -1101,7 +1110,7 @@
       <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="7" t="s">
         <v>63</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -1112,7 +1121,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -1131,7 +1140,7 @@
       <c r="B28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="7" t="s">
         <v>64</v>
       </c>
       <c r="D28" s="4"/>
@@ -1155,7 +1164,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="63" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -1168,7 +1177,7 @@
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -1181,7 +1190,7 @@
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -1194,7 +1203,7 @@
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -1213,14 +1222,14 @@
       <c r="B34" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="6"/>
       <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -1237,7 +1246,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -1250,7 +1259,7 @@
       <c r="E36" s="4"/>
     </row>
     <row r="37" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -1263,7 +1272,7 @@
       <c r="E37" s="4"/>
     </row>
     <row r="38" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -1276,7 +1285,7 @@
       <c r="E38" s="4"/>
     </row>
     <row r="39" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -1295,7 +1304,7 @@
       <c r="B40" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="7" t="s">
         <v>76</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -1312,7 +1321,7 @@
       <c r="B41" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="7" t="s">
         <v>77</v>
       </c>
       <c r="D41" s="4"/>
@@ -1325,7 +1334,7 @@
       <c r="B42" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="7" t="s">
         <v>78</v>
       </c>
       <c r="D42" s="4"/>
@@ -1338,7 +1347,7 @@
       <c r="B43" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="7" t="s">
         <v>79</v>
       </c>
       <c r="D43" s="4"/>
@@ -1351,7 +1360,7 @@
       <c r="B44" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="7" t="s">
         <v>80</v>
       </c>
       <c r="D44" s="4"/>
@@ -1364,7 +1373,7 @@
       <c r="B45" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D45" s="4"/>
@@ -1377,14 +1386,14 @@
       <c r="B46" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="7" t="s">
         <v>83</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
     </row>
     <row r="47" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -1397,7 +1406,7 @@
       <c r="E47" s="4"/>
     </row>
     <row r="48" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -1414,7 +1423,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -1427,7 +1436,7 @@
       <c r="E49" s="4"/>
     </row>
     <row r="50" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -1446,14 +1455,14 @@
       <c r="B51" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="7" t="s">
         <v>87</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
     </row>
     <row r="52" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -1466,7 +1475,7 @@
       <c r="E52" s="4"/>
     </row>
     <row r="53" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="5">
+      <c r="A53" s="8">
         <v>45717</v>
       </c>
       <c r="B53" s="4" t="s">
